--- a/data/trans_camb/P37-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P37-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 9,24</t>
+          <t>1,17; 9,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 6,3</t>
+          <t>-1,76; 5,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,17; 20,96</t>
+          <t>11,6; 20,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 7,78</t>
+          <t>-0,02; 8,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 6,71</t>
+          <t>-1,35; 7,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,99; 26,91</t>
+          <t>18,95; 26,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,42</t>
+          <t>1,81; 7,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,07</t>
+          <t>-0,38; 5,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,62; 22,7</t>
+          <t>16,41; 22,8</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 70,14</t>
+          <t>6,56; 65,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 45,45</t>
+          <t>-11,24; 42,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,39; 155,81</t>
+          <t>66,83; 151,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 58,75</t>
+          <t>-0,82; 63,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 52,19</t>
+          <t>-7,67; 55,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>109,08; 208,32</t>
+          <t>112,26; 211,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,83; 54,47</t>
+          <t>11,16; 55,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 37,07</t>
+          <t>-2,41; 37,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98,6; 163,77</t>
+          <t>98,2; 167,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 6,94</t>
+          <t>0,05; 6,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,33</t>
+          <t>-2,58; 3,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 14,16</t>
+          <t>-4,36; 14,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 6,13</t>
+          <t>-1,22; 5,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 5,42</t>
+          <t>-1,67; 5,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,74; 23,12</t>
+          <t>15,73; 22,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,35</t>
+          <t>0,76; 5,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,53</t>
+          <t>-1,5; 3,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 17,31</t>
+          <t>3,26; 17,26</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 54,59</t>
+          <t>0,82; 56,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 26,82</t>
+          <t>-15,74; 29,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 108,49</t>
+          <t>-29,14; 107,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 42,06</t>
+          <t>-7,21; 39,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 37,16</t>
+          <t>-9,45; 37,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,8; 162,98</t>
+          <t>86,17; 161,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 38,64</t>
+          <t>4,04; 41,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 24,9</t>
+          <t>-9,15; 24,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,52; 118,68</t>
+          <t>21,69; 118,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 6,49</t>
+          <t>-0,94; 6,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 7,61</t>
+          <t>-0,04; 7,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,62; 21,25</t>
+          <t>12,12; 21,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 4,94</t>
+          <t>-2,81; 5,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 3,43</t>
+          <t>-4,71; 3,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,86; 54,05</t>
+          <t>13,41; 58,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,83</t>
+          <t>-0,92; 4,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,59</t>
+          <t>-1,15; 4,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,58; 45,48</t>
+          <t>15,12; 45,81</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 57,8</t>
+          <t>-6,67; 59,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 69,85</t>
+          <t>0,05; 66,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,24; 190,44</t>
+          <t>80,61; 193,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 35,59</t>
+          <t>-16,11; 35,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 24,23</t>
+          <t>-25,4; 24,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82,55; 381,47</t>
+          <t>78,06; 402,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 36,71</t>
+          <t>-6,0; 35,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 36,01</t>
+          <t>-7,33; 32,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103,73; 318,64</t>
+          <t>100,07; 341,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,95</t>
+          <t>0,85; 7,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,95</t>
+          <t>-1,5; 4,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,99; 26,65</t>
+          <t>18,9; 26,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,91</t>
+          <t>-1,48; 5,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,98</t>
+          <t>-1,71; 5,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,97; 24,29</t>
+          <t>13,18; 24,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,26</t>
+          <t>0,84; 5,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,08</t>
+          <t>-0,64; 4,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,11; 24,23</t>
+          <t>16,89; 24,2</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,53; 58,7</t>
+          <t>5,46; 64,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 42,55</t>
+          <t>-8,93; 41,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126,38; 224,22</t>
+          <t>124,23; 219,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 42,17</t>
+          <t>-8,73; 35,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 34,13</t>
+          <t>-9,9; 36,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,59; 169,73</t>
+          <t>78,15; 169,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,72; 38,65</t>
+          <t>5,24; 39,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 30,17</t>
+          <t>-4,02; 29,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>110,55; 179,73</t>
+          <t>108,58; 178,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,52</t>
+          <t>2,07; 5,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,54</t>
+          <t>0,14; 3,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,72; 18,08</t>
+          <t>8,78; 17,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,21</t>
+          <t>0,56; 4,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,34</t>
+          <t>-0,35; 3,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,03; 34,67</t>
+          <t>18,64; 34,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,41</t>
+          <t>1,87; 4,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,85</t>
+          <t>0,37; 2,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,72; 25,55</t>
+          <t>15,95; 25,34</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12,08; 41,7</t>
+          <t>14,3; 43,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,03; 27,47</t>
+          <t>0,89; 27,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64,99; 135,45</t>
+          <t>65,13; 136,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2,69; 28,77</t>
+          <t>3,55; 29,74</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 22,62</t>
+          <t>-2,03; 23,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>117,58; 225,88</t>
+          <t>113,01; 222,75</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,77; 30,65</t>
+          <t>12,12; 30,69</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,22; 19,99</t>
+          <t>2,44; 19,97</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>102,76; 171,68</t>
+          <t>104,16; 173,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P37-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P37-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16,41</t>
+          <t>16,89</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,96</t>
+          <t>22,59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19,78</t>
+          <t>19,82</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 9,13</t>
+          <t>0,71; 9,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 5,83</t>
+          <t>-2,35; 5,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 20,77</t>
+          <t>12,48; 21,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 8,31</t>
+          <t>0,41; 8,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 7,03</t>
+          <t>-1,08; 7,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,95; 26,8</t>
+          <t>18,67; 26,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,53</t>
+          <t>1,57; 7,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,09</t>
+          <t>-0,41; 4,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,41; 22,8</t>
+          <t>16,67; 22,75</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107,59%</t>
+          <t>110,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>154,57%</t>
+          <t>152,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>131,37%</t>
+          <t>131,67%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 65,69</t>
+          <t>3,93; 71,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 42,69</t>
+          <t>-14,09; 40,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,83; 151,51</t>
+          <t>70,03; 159,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 63,93</t>
+          <t>2,49; 61,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 55,21</t>
+          <t>-6,25; 53,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>112,26; 211,55</t>
+          <t>109,89; 208,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 55,16</t>
+          <t>9,89; 53,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 37,28</t>
+          <t>-2,5; 35,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98,2; 167,37</t>
+          <t>99,86; 165,93</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>12,76</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,56</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,79</t>
+          <t>16,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 6,93</t>
+          <t>0,47; 7,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,7</t>
+          <t>-2,85; 3,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 14,45</t>
+          <t>9,36; 16,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,71</t>
+          <t>-1,26; 5,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 5,34</t>
+          <t>-1,71; 5,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,73; 22,91</t>
+          <t>15,81; 22,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,81</t>
+          <t>0,68; 5,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,39</t>
+          <t>-1,11; 3,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 17,26</t>
+          <t>13,51; 18,6</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>120,2%</t>
+          <t>119,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>106,53%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 56,36</t>
+          <t>2,09; 55,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 29,92</t>
+          <t>-18,46; 27,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 107,48</t>
+          <t>58,6; 133,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 39,66</t>
+          <t>-6,69; 38,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 37,0</t>
+          <t>-9,78; 36,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,17; 161,93</t>
+          <t>87,16; 156,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 41,63</t>
+          <t>4,16; 39,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 24,34</t>
+          <t>-6,79; 25,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,69; 118,07</t>
+          <t>80,46; 134,25</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,89</t>
+          <t>16,78</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,39</t>
+          <t>15,89</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>16,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 6,62</t>
+          <t>-1,32; 6,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 7,45</t>
+          <t>-0,5; 7,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,12; 21,41</t>
+          <t>12,28; 20,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 5,16</t>
+          <t>-2,9; 5,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 3,45</t>
+          <t>-4,35; 3,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,41; 58,27</t>
+          <t>11,7; 19,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,76</t>
+          <t>-1,08; 4,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,41</t>
+          <t>-1,15; 4,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,12; 45,81</t>
+          <t>13,21; 19,36</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130,38%</t>
+          <t>129,55%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>188,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>170,59%</t>
+          <t>112,41%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 59,55</t>
+          <t>-9,21; 55,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,05; 66,06</t>
+          <t>-3,4; 64,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80,61; 193,39</t>
+          <t>82,06; 194,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 35,95</t>
+          <t>-16,15; 38,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,4; 24,36</t>
+          <t>-24,4; 25,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78,06; 402,42</t>
+          <t>63,34; 143,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 35,92</t>
+          <t>-6,97; 34,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 32,88</t>
+          <t>-7,32; 32,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100,07; 341,43</t>
+          <t>82,11; 150,01</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22,69</t>
+          <t>22,04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,29</t>
+          <t>22,3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21,43</t>
+          <t>22,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,6</t>
+          <t>0,48; 7,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 4,91</t>
+          <t>-1,11; 5,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,9; 26,77</t>
+          <t>18,28; 25,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 5,32</t>
+          <t>-0,84; 5,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 5,3</t>
+          <t>-1,7; 4,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,18; 24,56</t>
+          <t>18,95; 25,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,35</t>
+          <t>0,75; 5,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,04</t>
+          <t>-0,73; 3,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,89; 24,2</t>
+          <t>19,82; 24,75</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>169,0%</t>
+          <t>164,14%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>127,17%</t>
+          <t>139,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>145,29%</t>
+          <t>150,45%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,46; 64,37</t>
+          <t>1,97; 62,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 41,79</t>
+          <t>-7,35; 42,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>124,23; 219,84</t>
+          <t>120,12; 215,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 35,91</t>
+          <t>-4,64; 40,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 36,48</t>
+          <t>-9,62; 35,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,15; 169,13</t>
+          <t>105,18; 185,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,24; 39,04</t>
+          <t>4,89; 41,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 29,3</t>
+          <t>-4,68; 28,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>108,58; 178,18</t>
+          <t>122,74; 182,95</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>17,04</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,19</t>
+          <t>20,14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>19,28</t>
+          <t>18,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,46</t>
+          <t>1,81; 5,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,63</t>
+          <t>0,29; 3,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,78; 17,98</t>
+          <t>15,07; 19,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,36</t>
+          <t>0,6; 4,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,48</t>
+          <t>-0,58; 3,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,64; 34,33</t>
+          <t>18,28; 22,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,4</t>
+          <t>1,75; 4,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,85</t>
+          <t>0,32; 2,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,95; 25,34</t>
+          <t>17,32; 20,0</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108,98%</t>
+          <t>122,81%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>146,28%</t>
+          <t>127,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>129,58%</t>
+          <t>125,33%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>14,3; 43,22</t>
+          <t>12,15; 41,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,89; 27,72</t>
+          <t>2,07; 27,78</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65,13; 136,27</t>
+          <t>101,39; 146,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3,55; 29,74</t>
+          <t>3,08; 27,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 23,53</t>
+          <t>-3,42; 22,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>113,01; 222,75</t>
+          <t>108,86; 150,15</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,12; 30,69</t>
+          <t>11,45; 30,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,44; 19,97</t>
+          <t>1,99; 19,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>104,16; 173,49</t>
+          <t>109,33; 139,98</t>
         </is>
       </c>
     </row>
